--- a/data/Date_Sector_Public.xlsx
+++ b/data/Date_Sector_Public.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11008"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/63791cb58948d71e/Desktop/Dash/dashboard_excel_final/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/air/Desktop/FrameworkData-main/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_EA5C7247947CEA4EE01C78155A4486B868DED767" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65CD662D-8644-4127-860D-B25CE6CF24C0}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3CFEFBC-9111-C54B-8BC1-DFC4BF8BC916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Public" sheetId="1" r:id="rId1"/>
@@ -34,10 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
-  <si>
-    <t>Sector Public — Date anuale Min. Finantelor (completati cu date oficiale)</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>An</t>
   </si>
@@ -55,6 +52,60 @@
   </si>
   <si>
     <t>Datorie totală (% PIB)</t>
+  </si>
+  <si>
+    <t>31.4</t>
+  </si>
+  <si>
+    <t>36.7</t>
+  </si>
+  <si>
+    <t>-5.3</t>
+  </si>
+  <si>
+    <t>32.0</t>
+  </si>
+  <si>
+    <t>33.9</t>
+  </si>
+  <si>
+    <t>-1.9</t>
+  </si>
+  <si>
+    <t>33.3</t>
+  </si>
+  <si>
+    <t>36.6</t>
+  </si>
+  <si>
+    <t>-3.2</t>
+  </si>
+  <si>
+    <t>33.7</t>
+  </si>
+  <si>
+    <t>38.8</t>
+  </si>
+  <si>
+    <t>-5.1</t>
+  </si>
+  <si>
+    <t>34.3</t>
+  </si>
+  <si>
+    <t>38.7</t>
+  </si>
+  <si>
+    <t>-4.4</t>
+  </si>
+  <si>
+    <t>34.2</t>
+  </si>
+  <si>
+    <t>38.3</t>
+  </si>
+  <si>
+    <t>-4.1</t>
   </si>
 </sst>
 </file>
@@ -62,22 +113,15 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -99,23 +143,26 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF185FA5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6E4F7"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -139,21 +186,20 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="3" fillId="4" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
@@ -458,204 +504,290 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="21" customWidth="1"/>
     <col min="4" max="4" width="23" customWidth="1"/>
     <col min="5" max="6" width="26" customWidth="1"/>
-    <col min="7" max="8" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="10.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="1" t="s">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>2019</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="2">
+        <v>25.449218910012092</v>
+      </c>
+      <c r="F2" s="2">
+        <v>14.216484063571889</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2020</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2019</v>
-      </c>
-      <c r="B3" s="6">
-        <v>31.2</v>
-      </c>
-      <c r="C3" s="6">
-        <v>32.1</v>
-      </c>
-      <c r="D3" s="6">
-        <v>-0.9</v>
-      </c>
-      <c r="E3" s="5">
-        <v>25.449218910012092</v>
-      </c>
-      <c r="F3" s="5">
-        <v>14.216484063571889</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2">
+        <v>33.955582225579931</v>
+      </c>
+      <c r="F3" s="2">
+        <v>19.318280987997998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>2020</v>
-      </c>
-      <c r="B4" s="6">
-        <v>31.8</v>
-      </c>
-      <c r="C4" s="6">
-        <v>35.4</v>
-      </c>
-      <c r="D4" s="6">
-        <v>-3.6</v>
-      </c>
-      <c r="E4" s="5">
-        <v>33.955582225579931</v>
-      </c>
-      <c r="F4" s="5">
-        <v>19.318280987997998</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+        <v>2021</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="2">
+        <v>32.118749201938016</v>
+      </c>
+      <c r="F4" s="2">
+        <v>18.370578974156366</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5">
-        <v>2021</v>
-      </c>
-      <c r="B5" s="6">
-        <v>34.5</v>
-      </c>
-      <c r="C5" s="6">
-        <v>37.799999999999997</v>
-      </c>
-      <c r="D5" s="6">
-        <v>-3.3</v>
-      </c>
-      <c r="E5" s="5">
-        <v>32.118749201938016</v>
-      </c>
-      <c r="F5" s="5">
-        <v>18.370578974156366</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+        <v>2022</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="2">
+        <v>34.486053373748916</v>
+      </c>
+      <c r="F5" s="2">
+        <v>21.919969592000349</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>2022</v>
-      </c>
-      <c r="B6" s="6">
-        <v>36.200000000000003</v>
-      </c>
-      <c r="C6" s="6">
-        <v>39.1</v>
-      </c>
-      <c r="D6" s="6">
-        <v>-2.9</v>
-      </c>
-      <c r="E6" s="5">
-        <v>34.486053373748916</v>
-      </c>
-      <c r="F6" s="5">
-        <v>21.919969592000349</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+        <v>2023</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="2">
+        <v>34.261810742244187</v>
+      </c>
+      <c r="F6" s="2">
+        <v>21.194575576688589</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>2023</v>
-      </c>
-      <c r="B7" s="6">
-        <v>37.1</v>
-      </c>
-      <c r="C7" s="6">
-        <v>40.5</v>
-      </c>
-      <c r="D7" s="6">
-        <v>-3.4</v>
-      </c>
-      <c r="E7" s="5">
-        <v>34.261810742244187</v>
-      </c>
-      <c r="F7" s="5">
-        <v>21.194575576688589</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+        <v>2024</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="2">
+        <v>37.488966251512018</v>
+      </c>
+      <c r="F7" s="2">
+        <v>23.913025567373065</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8">
-        <v>2024</v>
-      </c>
-      <c r="B8" s="6">
-        <v>37.799999999999997</v>
-      </c>
-      <c r="C8" s="6">
-        <v>41.2</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-3.4</v>
-      </c>
-      <c r="E8" s="5">
-        <v>37.488966251512018</v>
-      </c>
-      <c r="F8" s="5">
-        <v>23.913025567373065</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9">
         <v>2025</v>
       </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="5">
+      <c r="B8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="2">
         <v>37.558469260070552</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F8" s="2">
         <v>22.850757962132992</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" s="5"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" s="5"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" s="5"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21" s="5"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" s="5"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23" s="5"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A24" s="5"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25" s="5"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>